--- a/Result/profitability/1541.xlsx
+++ b/Result/profitability/1541.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.26</v>
       </c>
       <c r="M2" t="n">
-        <v>0.30625</v>
+        <v>0.34625</v>
       </c>
       <c r="N2" t="n">
-        <v>16.715</v>
+        <v>17.21875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.23</v>
       </c>
       <c r="M3" t="n">
-        <v>0.30375</v>
+        <v>0.30125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.2375</v>
+        <v>15.01875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3675</v>
+        <v>0.315</v>
       </c>
       <c r="N4" t="n">
-        <v>14.32875</v>
+        <v>14.0275</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3462500000000001</v>
+        <v>0.4</v>
       </c>
       <c r="N5" t="n">
-        <v>13.64</v>
+        <v>13.42875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,13 +1137,13 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4225</v>
+        <v>0.29875</v>
       </c>
       <c r="N6" t="n">
-        <v>13.0825</v>
+        <v>13.34625</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>0.36875</v>
+        <v>0.2575</v>
       </c>
       <c r="N7" t="n">
-        <v>14.38375</v>
+        <v>14.1175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3675</v>
+        <v>0.32125</v>
       </c>
       <c r="N8" t="n">
-        <v>14.87</v>
+        <v>14.705</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1541</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>603</v>
+      </c>
+      <c r="D75" t="n">
+        <v>498</v>
+      </c>
+      <c r="E75" t="n">
+        <v>105</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>17</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.815</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7708333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.319999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07043756670224099</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.34375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.689999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08843537414965974</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
